--- a/public/converted/nomenklatura-weissgauff-v-zagruzku-1c.xlsx
+++ b/public/converted/nomenklatura-weissgauff-v-zagruzku-1c.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товары'!$A$2:$H$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товары'!$A$2:$H$161</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -439,7 +439,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Номенклатура ООО "ВГ-ТРЕЙД" (Weissgauff), счёт № 1222 от 20.10.2026 + УПД № 261019009/2 от 19.10.2026, в загрузку 1С</t>
+          <t>Номенклатура ООО "ВГ-ТРЕЙД" (Weissgauff), счета № 1222 и № 1223 от 20.10.2026 + УПД № 261019009/2 и № 261019008/2 от 19.10.2026, в загрузку 1С</t>
         </is>
       </c>
     </row>
@@ -518,17 +518,17 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>439258</t>
+          <t>433585</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>4393720606963</t>
+          <t>4393720600619</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff Cover 50 Black</t>
+          <t>Вытяжка Weissgauff Box 40 PB White</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -548,17 +548,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>439259</t>
+          <t>439258</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>4393720606970</t>
+          <t>4393720606963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff Cover 50 White</t>
+          <t>Вытяжка Weissgauff Cover 50 Black</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -578,17 +578,17 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>439209</t>
+          <t>439259</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>4393720606574</t>
+          <t>4393720606970</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff Cover 500 White</t>
+          <t>Вытяжка Weissgauff Cover 50 White</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -608,17 +608,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>439048</t>
+          <t>439209</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>4393720606017</t>
+          <t>4393720606574</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff Cover 600 Black</t>
+          <t>Вытяжка Weissgauff Cover 500 White</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -638,17 +638,17 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>439264</t>
+          <t>439048</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>4393720606635</t>
+          <t>4393720606017</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff TEL 06 1M BM</t>
+          <t>Вытяжка Weissgauff Cover 600 Black</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -668,17 +668,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>430020</t>
+          <t>439264</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>4393720468912</t>
+          <t>4393720606635</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff TEL 450 EW</t>
+          <t>Вытяжка Weissgauff TEL 06 1M BM</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -698,17 +698,17 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>438286</t>
+          <t>439265</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>4393720604587</t>
+          <t>4393720606642</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff TEL 450 White Glass</t>
+          <t>Вытяжка Weissgauff TEL 06 1M WM</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -728,17 +728,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>438277</t>
+          <t>430020</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>4393720604594</t>
+          <t>4393720468912</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff TEL 500 Black Glass</t>
+          <t>Вытяжка Weissgauff TEL 450 EW</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -758,17 +758,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>438283</t>
+          <t>438286</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>4393720604631</t>
+          <t>4393720604587</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff TEL 600 2M Touch White Glass</t>
+          <t>Вытяжка Weissgauff TEL 450 White Glass</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -788,17 +788,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>436620</t>
+          <t>438277</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>4393720602804</t>
+          <t>4393720604594</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff TEL 600 Black Glass</t>
+          <t>Вытяжка Weissgauff TEL 500 Black Glass</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -818,17 +818,17 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>436624</t>
+          <t>438283</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>4393720602828</t>
+          <t>4393720604631</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff TEL 600 TC BL</t>
+          <t>Вытяжка Weissgauff TEL 600 2M Touch White Glass</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -848,17 +848,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>436623</t>
+          <t>436620</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>4393720602811</t>
+          <t>4393720602804</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff TEL 600 White Glass</t>
+          <t>Вытяжка Weissgauff TEL 600 Black Glass</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -878,17 +878,17 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>431736</t>
+          <t>430026</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>4393720474951</t>
+          <t>4393720468967</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff Zaurak 50 PB WH</t>
+          <t>Вытяжка Weissgauff TEL 600 EW</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -908,17 +908,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>430899</t>
+          <t>436624</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>4393720472537</t>
+          <t>4393720602828</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Вытяжка Weissgauff Zosma 50 PB WH</t>
+          <t>Вытяжка Weissgauff TEL 600 TC BL</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -938,17 +938,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>440036</t>
+          <t>436623</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>4393720608738</t>
+          <t>4393720602811</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Газовая панель Weissgauff HG 451 BFh</t>
+          <t>Вытяжка Weissgauff TEL 600 White Glass</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -956,7 +956,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Газовая панель</t>
+          <t>Вытяжка</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -968,17 +968,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>395117</t>
+          <t>431736</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>4393720472513</t>
+          <t>4393720474951</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Газовая панель Weissgauff HG 640 BG</t>
+          <t>Вытяжка Weissgauff Zaurak 50 PB WH</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Газовая панель</t>
+          <t>Вытяжка</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -998,17 +998,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>433581</t>
+          <t>430899</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>4393720600565</t>
+          <t>4393720472537</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Газовая панель Weissgauff HG 640 BGh</t>
+          <t>Вытяжка Weissgauff Zosma 50 PB WH</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Газовая панель</t>
+          <t>Вытяжка</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1028,17 +1028,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>430951</t>
+          <t>430946</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>4393720472520</t>
+          <t>4393720472476</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Газовая панель Weissgauff HG 640 WG</t>
+          <t>Газовая панель Weissgauff HG 430 WGH</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1058,17 +1058,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>433582</t>
+          <t>440036</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>4393720600572</t>
+          <t>4393720608738</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Газовая панель Weissgauff HG 640 WGh</t>
+          <t>Газовая панель Weissgauff HG 451 BFh</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1088,17 +1088,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>440032</t>
+          <t>442140</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>4393720608776</t>
+          <t>4670239260085</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Газовая панель Weissgauff HG 641 BFh</t>
+          <t>Газовая панель Weissgauff HG 453 XFH</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1118,17 +1118,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>433085</t>
+          <t>395117</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>4393720477686</t>
+          <t>4393720472513</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Газовая панель Weissgauff HGG 640 BG Nano Glass</t>
+          <t>Газовая панель Weissgauff HG 640 BG</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1148,17 +1148,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>442266</t>
+          <t>433581</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>4670239260801</t>
+          <t>4393720600565</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Газовая панель Weissgauff HGG 641 BGSH</t>
+          <t>Газовая панель Weissgauff HG 640 BGh</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1178,17 +1178,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>411843</t>
+          <t>430951</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>4393720445456</t>
+          <t>4393720472520</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Газовая панель Weissgauff HGG 641 Xh</t>
+          <t>Газовая панель Weissgauff HG 640 WG</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1208,17 +1208,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>438316</t>
+          <t>433582</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>4393720605263</t>
+          <t>4393720600572</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Газовая плита Weissgauff WGSM 5000 B</t>
+          <t>Газовая панель Weissgauff HG 640 WGh</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Газовая плита</t>
+          <t>Газовая панель</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1238,17 +1238,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>433108</t>
+          <t>433218</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>4393720478034</t>
+          <t>4393720600190</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Духовой шкаф Weissgauff EOM 108 PDB</t>
+          <t>Газовая панель Weissgauff HG 640 WGV</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Духовой шкаф</t>
+          <t>Газовая панель</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1268,17 +1268,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>333534</t>
+          <t>440032</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>4393720470885</t>
+          <t>4393720608776</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Духовой шкаф Weissgauff EOM 180 B</t>
+          <t>Газовая панель Weissgauff HG 641 BFh</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Духовой шкаф</t>
+          <t>Газовая панель</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1298,17 +1298,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>433111</t>
+          <t>433084</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>4393720478065</t>
+          <t>4393720477679</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Духовой шкаф Weissgauff EOM 208 PDB Steam Clean</t>
+          <t>Газовая панель Weissgauff HGG 451 BFh Nano Matt Glass</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Духовой шкаф</t>
+          <t>Газовая панель</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1328,17 +1328,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>433112</t>
+          <t>433085</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>4393720478072</t>
+          <t>4393720477686</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Духовой шкаф Weissgauff EOM 208 PDW Steam Clean</t>
+          <t>Газовая панель Weissgauff HGG 640 BG Nano Glass</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Духовой шкаф</t>
+          <t>Газовая панель</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1358,17 +1358,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>438036</t>
+          <t>411841</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>4393720604464</t>
+          <t>4393720445432</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Духовой шкаф Weissgauff EOM 710 SW</t>
+          <t>Газовая панель Weissgauff HGG 641 BGh</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Духовой шкаф</t>
+          <t>Газовая панель</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1388,17 +1388,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>423158</t>
+          <t>442266</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>4393720450696</t>
+          <t>4670239260801</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Духовой шкаф Weissgauff EOV 19 MB</t>
+          <t>Газовая панель Weissgauff HGG 641 BGSH</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Духовой шкаф</t>
+          <t>Газовая панель</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1418,17 +1418,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>423984</t>
+          <t>433087</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>4393720451006</t>
+          <t>4393720477709</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Духовой шкаф Weissgauff EOV 19 MW</t>
+          <t>Газовая панель Weissgauff HGG 641 BV Nano Matt Glass</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Духовой шкаф</t>
+          <t>Газовая панель</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1448,17 +1448,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>436718</t>
+          <t>411843</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>4393720602729</t>
+          <t>4393720445456</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Духовой шкаф Weissgauff EOV 29 PDBS Black Edition</t>
+          <t>Газовая панель Weissgauff HGG 641 Xh</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Духовой шкаф</t>
+          <t>Газовая панель</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1478,17 +1478,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>434927</t>
+          <t>324599</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>4393720601494</t>
+          <t>4393720467960</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Духовой шкаф Weissgauff EOV 799 SB</t>
+          <t>Газовая панель Weissgauff HGRG 641 BG</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Духовой шкаф</t>
+          <t>Газовая панель</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1508,17 +1508,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>431395</t>
+          <t>438316</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>4393720473398</t>
+          <t>4393720605263</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Духовой шкаф Weissgauff EOY 456 XM</t>
+          <t>Газовая плита Weissgauff WGSM 5000 B</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Духовой шкаф</t>
+          <t>Газовая плита</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1538,17 +1538,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>437402</t>
+          <t>439051</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>4393720603573</t>
+          <t>4393720605904</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Микроволновая печь Weissgauff BMWO-206</t>
+          <t>Духовой шкаф Weissgauff EOM 104 W</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Микроволновая печь</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1568,17 +1568,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>431799</t>
+          <t>433108</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>4393720475194</t>
+          <t>4393720478034</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Микроволновая печь Weissgauff HMT-2012 Grill</t>
+          <t>Духовой шкаф Weissgauff EOM 108 PDB</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Микроволновая печь</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1598,17 +1598,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>436314</t>
+          <t>333534</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>4393720602736</t>
+          <t>4393720470885</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Микроволновая печь Weissgauff HMT-256 TSB</t>
+          <t>Духовой шкаф Weissgauff EOM 180 B</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Микроволновая печь</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1628,17 +1628,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>437857</t>
+          <t>437405</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>4393720604112</t>
+          <t>4393720603597</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Микроволновая печь Weissgauff HMT-452 D</t>
+          <t>Духовой шкаф Weissgauff EOM 206 BM</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Микроволновая печь</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1658,17 +1658,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>437853</t>
+          <t>433111</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>4393720604082</t>
+          <t>4393720478065</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Микроволновая печь Weissgauff HMT-456</t>
+          <t>Духовой шкаф Weissgauff EOM 208 PDB Steam Clean</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Микроволновая печь</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1688,17 +1688,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>437855</t>
+          <t>433112</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>4393720604099</t>
+          <t>4393720478072</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Микроволновая печь Weissgauff HMT-456 D</t>
+          <t>Духовой шкаф Weissgauff EOM 208 PDW Steam Clean</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Микроволновая печь</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1718,17 +1718,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>440299</t>
+          <t>438036</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>4393720609001</t>
+          <t>4393720604464</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Морозильник Weissgauff WFH-150 Inverter</t>
+          <t>Духовой шкаф Weissgauff EOM 710 SW</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Морозильник</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1748,17 +1748,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>440302</t>
+          <t>431584</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>4393720609032</t>
+          <t>4393720473916</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Морозильник Weissgauff WFH-300 Inverter</t>
+          <t>Духовой шкаф Weissgauff EOM 751 PDB Black Edition</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Морозильник</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1778,17 +1778,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>440303</t>
+          <t>423158</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>4393720609049</t>
+          <t>4393720450696</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Морозильник Weissgauff WFH-360 Inverter</t>
+          <t>Духовой шкаф Weissgauff EOV 19 MB</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Морозильник</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1808,17 +1808,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>441229</t>
+          <t>423984</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>4393720610335</t>
+          <t>4393720451006</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Морозильник Weissgauff WFH-450</t>
+          <t>Духовой шкаф Weissgauff EOV 19 MW</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Морозильник</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1838,17 +1838,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>439601</t>
+          <t>436718</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>4393720607397</t>
+          <t>4393720602729</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Морозильник Weissgauff WRF-80 Defrost Black</t>
+          <t>Духовой шкаф Weissgauff EOV 29 PDBS Black Edition</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Морозильник</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -1868,17 +1868,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>432979</t>
+          <t>434927</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>4393720477891</t>
+          <t>4393720601494</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Посудомоечная машина Weissgauff BDW 4536 D</t>
+          <t>Духовой шкаф Weissgauff EOV 799 SB</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Посудомоечная машина</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1898,17 +1898,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>441239</t>
+          <t>426774</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>4393720610342</t>
+          <t>4393720463047</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Посудомоечная машина Weissgauff BDW 4538 Timer Floor</t>
+          <t>Духовой шкаф Weissgauff EOY 451 PDX</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Посудомоечная машина</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -1928,17 +1928,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>441089</t>
+          <t>431395</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>4393720609926</t>
+          <t>4393720473398</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Посудомоечная машина Weissgauff BDW 6151 Inverter Touch AutoOpen Infolight</t>
+          <t>Духовой шкаф Weissgauff EOY 456 XM</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Посудомоечная машина</t>
+          <t>Духовой шкаф</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -1958,17 +1958,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>419435</t>
+          <t>439143</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>4393720447924</t>
+          <t>4393720604938</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Посудомоечная машина Weissgauff DW 4015</t>
+          <t>Кофемашина Weissgauff WCM-335 Automatic ColorTouch Cappuccino Nero</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Посудомоечная машина</t>
+          <t>Кофемашина</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -1988,17 +1988,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>439781</t>
+          <t>437402</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>4393720608523</t>
+          <t>4393720603573</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Посудомоечная машина Weissgauff DW 4508 Inverter Autoopen Black</t>
+          <t>Микроволновая печь Weissgauff BMWO-206</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Посудомоечная машина</t>
+          <t>Микроволновая печь</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2018,17 +2018,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>433792</t>
+          <t>431799</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>4393720600763</t>
+          <t>4393720475194</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Посудомоечная машина Weissgauff DW 4535</t>
+          <t>Микроволновая печь Weissgauff HMT-2012 Grill</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Посудомоечная машина</t>
+          <t>Микроволновая печь</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2048,17 +2048,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>419440</t>
+          <t>436314</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>4393720447931</t>
+          <t>4393720602736</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Посудомоечная машина Weissgauff DW 6015</t>
+          <t>Микроволновая печь Weissgauff HMT-256 TSB</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Посудомоечная машина</t>
+          <t>Микроволновая печь</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2078,17 +2078,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>437357</t>
+          <t>437856</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>4393720603443</t>
+          <t>4393720604105</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Посудомоечная машина Weissgauff DW 6038 Autoopen</t>
+          <t>Микроволновая печь Weissgauff HMT-452</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Посудомоечная машина</t>
+          <t>Микроволновая печь</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2108,17 +2108,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>437360</t>
+          <t>437857</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>4393720603962</t>
+          <t>4393720604112</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Посудомоечная машина Weissgauff DW 6038 X Inverter</t>
+          <t>Микроволновая печь Weissgauff HMT-452 D</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Посудомоечная машина</t>
+          <t>Микроволновая печь</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2138,17 +2138,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>425987</t>
+          <t>437853</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>4393720458876</t>
+          <t>4393720604082</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Посудомоечная машина Weissgauff TDW 4006 D</t>
+          <t>Микроволновая печь Weissgauff HMT-456</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Посудомоечная машина</t>
+          <t>Микроволновая печь</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2168,17 +2168,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>419432</t>
+          <t>437855</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>4393720447917</t>
+          <t>4393720604099</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Посудомоечная машина Weissgauff TDW 4017 D</t>
+          <t>Микроволновая печь Weissgauff HMT-456 D</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Посудомоечная машина</t>
+          <t>Микроволновая печь</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2198,17 +2198,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>432284</t>
+          <t>440299</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>4393720476184</t>
+          <t>4393720609001</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Стеклокерамическая плита Weissgauff WES E2V05 S</t>
+          <t>Морозильник Weissgauff WFH-150 Inverter</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Стеклокерамическая плита</t>
+          <t>Морозильник</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2228,17 +2228,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>438325</t>
+          <t>440302</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>4393720605355</t>
+          <t>4393720609032</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Стеклокерамическая плита Weissgauff WESM 5240 B</t>
+          <t>Морозильник Weissgauff WFH-300 Inverter</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Стеклокерамическая плита</t>
+          <t>Морозильник</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2258,17 +2258,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>438328</t>
+          <t>440303</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>4393720605386</t>
+          <t>4393720609049</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Стеклокерамическая плита Weissgauff WESM 5260 B</t>
+          <t>Морозильник Weissgauff WFH-360 Inverter</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Стеклокерамическая плита</t>
+          <t>Морозильник</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2288,17 +2288,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>438329</t>
+          <t>441229</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>4393720605393</t>
+          <t>4393720610335</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Стеклокерамическая плита Weissgauff WESM 5260 X</t>
+          <t>Морозильник Weissgauff WFH-450</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Стеклокерамическая плита</t>
+          <t>Морозильник</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2318,17 +2318,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>440451</t>
+          <t>439601</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>4393720609094</t>
+          <t>4393720607397</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 39107 Full Touch Inverter Steam</t>
+          <t>Морозильник Weissgauff WRF-80 Defrost Black</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Морозильник</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2348,17 +2348,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>439783</t>
+          <t>439602</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>4393720608394</t>
+          <t>4393720607403</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 39107 Inverter Steam</t>
+          <t>Морозильник Weissgauff WRF-80 Defrost Dark Grey</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Морозильник</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2378,17 +2378,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>438789</t>
+          <t>432979</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>4393720605782</t>
+          <t>4393720477891</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 40106 Inverter Steam</t>
+          <t>Посудомоечная машина Weissgauff BDW 4536 D</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2408,17 +2408,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>430263</t>
+          <t>429861</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>4393720470373</t>
+          <t>4393720468332</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 40970 TD Inverter Steam</t>
+          <t>Посудомоечная машина Weissgauff BDW 4537</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2438,17 +2438,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>438965</t>
+          <t>441239</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>4393720605676</t>
+          <t>4393720610342</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 41106 Inverter Steam</t>
+          <t>Посудомоечная машина Weissgauff BDW 4538 Timer Floor</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2468,17 +2468,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>439707</t>
+          <t>432987</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>4393720607861</t>
+          <t>4393720478010</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 4506 Inverter Steam</t>
+          <t>Посудомоечная машина Weissgauff BDW 6025 D Infolight</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2498,17 +2498,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>431369</t>
+          <t>441089</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>4393720473282</t>
+          <t>4393720609926</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 4506 LED</t>
+          <t>Посудомоечная машина Weissgauff BDW 6151 Inverter Touch AutoOpen Infolight</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -2528,17 +2528,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>432584</t>
+          <t>419435</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>4393720476603</t>
+          <t>4393720447924</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 45127 DC Inverter Steam</t>
+          <t>Посудомоечная машина Weissgauff DW 4015</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -2558,17 +2558,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>430972</t>
+          <t>439780</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>4393720472933</t>
+          <t>4393720608516</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 47147 DC Inverter Steam</t>
+          <t>Посудомоечная машина Weissgauff DW 4508 Inverter Autoopen</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -2588,17 +2588,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>436615</t>
+          <t>439781</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>4393720602798</t>
+          <t>4393720608523</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 47147 DC Inverter Steam Silver</t>
+          <t>Посудомоечная машина Weissgauff DW 4508 Inverter Autoopen Black</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -2618,17 +2618,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>438973</t>
+          <t>433792</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>4393720605706</t>
+          <t>4393720600763</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 48128 Inverter Steam</t>
+          <t>Посудомоечная машина Weissgauff DW 4535</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -2648,17 +2648,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>441512</t>
+          <t>419440</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>4393720610472</t>
+          <t>4393720447931</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 49128 Сolor Touch Inverter Steam</t>
+          <t>Посудомоечная машина Weissgauff DW 6015</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -2678,17 +2678,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>436159</t>
+          <t>431823</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>4393720602538</t>
+          <t>4393720475422</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 58411 Direct Drive Inverter Premium Steam Steel</t>
+          <t>Посудомоечная машина Weissgauff DW 6025</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2708,17 +2708,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>434764</t>
+          <t>437357</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>4393720601203</t>
+          <t>4393720603443</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WM 59411 Direct Drive Inverter Steam</t>
+          <t>Посудомоечная машина Weissgauff DW 6038 Autoopen</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -2738,17 +2738,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>433622</t>
+          <t>437358</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>4393720600671</t>
+          <t>4393720603948</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WMD 46148 DC Inverter Steam</t>
+          <t>Посудомоечная машина Weissgauff DW 6038 B Inverter</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2768,17 +2768,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>438586</t>
+          <t>437360</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>4393720605232</t>
+          <t>4393720603962</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WMD 4628 Inverter Steam</t>
+          <t>Посудомоечная машина Weissgauff DW 6038 X Inverter</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -2798,17 +2798,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>433417</t>
+          <t>437886</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>4393720600381</t>
+          <t>4393720604181</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WMD 58411 Direct Drive Inverter Premium Steam Grey</t>
+          <t>Посудомоечная машина Weissgauff DW 996 Touch Inverter Dual Fan Dry</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -2828,17 +2828,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>440884</t>
+          <t>425987</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>4393720609902</t>
+          <t>4393720458876</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Стиральная машина Weissgauff WMD 995 Autodose Direct Drive Touch</t>
+          <t>Посудомоечная машина Weissgauff TDW 4006 D</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Стиральная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -2858,17 +2858,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>438786</t>
+          <t>419432</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>4393720605799</t>
+          <t>4393720447917</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Сушильная машина Weissgauff WD 4948 Heat Pump</t>
+          <t>Посудомоечная машина Weissgauff TDW 4017 D</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Сушильная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -2888,17 +2888,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>433780</t>
+          <t>426645</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>4393720600787</t>
+          <t>4393720462897</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Сушильная машина Weissgauff WD 6110 B Heat Pump</t>
+          <t>Посудомоечная машина Weissgauff TDW 4037 D</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Сушильная машина</t>
+          <t>Посудомоечная машина</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -2918,17 +2918,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>429679</t>
+          <t>432284</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>4393720467670</t>
+          <t>4393720476184</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Сушильная машина Weissgauff WD 6128 D</t>
+          <t>Стеклокерамическая плита Weissgauff WES E2V05 S</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Сушильная машина</t>
+          <t>Стеклокерамическая плита</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -2948,17 +2948,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>432450</t>
+          <t>438322</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>4393720476504</t>
+          <t>4393720605324</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Сушильная машина Weissgauff WD 998 Heat Pump Full Touch Silver</t>
+          <t>Стеклокерамическая плита Weissgauff WESM 5140 B</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Сушильная машина</t>
+          <t>Стеклокерамическая плита</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -2978,17 +2978,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>433144</t>
+          <t>438325</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>4393720477433</t>
+          <t>4393720605355</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WFD 450 Built-in Inverter NoFrost Dark Inox</t>
+          <t>Стеклокерамическая плита Weissgauff WESM 5240 B</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стеклокерамическая плита</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3008,17 +3008,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>439610</t>
+          <t>438326</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>4393720607472</t>
+          <t>4393720605362</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WR-092 Defrost Dark Grey</t>
+          <t>Стеклокерамическая плита Weissgauff WESM 5240 X</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стеклокерамическая плита</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3038,17 +3038,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>441036</t>
+          <t>438328</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>4393720609995</t>
+          <t>4393720605386</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRI-85 Inverter</t>
+          <t>Стеклокерамическая плита Weissgauff WESM 5260 B</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стеклокерамическая плита</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3068,17 +3068,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>440021</t>
+          <t>438327</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>4393720608608</t>
+          <t>4393720605379</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 1275 DeFrost White</t>
+          <t>Стеклокерамическая плита Weissgauff WESM 5260 W</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стеклокерамическая плита</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3098,17 +3098,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>439613</t>
+          <t>438329</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>4393720607502</t>
+          <t>4393720605393</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 1430 Defrost Dark Grey</t>
+          <t>Стеклокерамическая плита Weissgauff WESM 5260 X</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стеклокерамическая плита</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3128,17 +3128,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>440022</t>
+          <t>438301</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>4393720608615</t>
+          <t>4393720604693</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 145 DeFrost Inox</t>
+          <t>Стиральная машина Weissgauff WM 39106 Inverter Steam</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3158,17 +3158,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>440023</t>
+          <t>440451</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>4393720608622</t>
+          <t>4393720609094</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 145 DeFrost White</t>
+          <t>Стиральная машина Weissgauff WM 39107 Full Touch Inverter Steam</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3188,17 +3188,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>442964</t>
+          <t>439783</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>4670239260887</t>
+          <t>4393720608394</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 1520 Defrost Black</t>
+          <t>Стиральная машина Weissgauff WM 39107 Inverter Steam</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3218,17 +3218,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>439568</t>
+          <t>438789</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>4393720607106</t>
+          <t>4393720605782</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 1520 Defrost White</t>
+          <t>Стиральная машина Weissgauff WM 40106 Inverter Steam</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3248,17 +3248,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>442286</t>
+          <t>430263</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>4670239260238</t>
+          <t>4393720470373</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 1650 Defrost Dark Grey</t>
+          <t>Стиральная машина Weissgauff WM 40970 TD Inverter Steam</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3278,17 +3278,17 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>440027</t>
+          <t>426826</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>4393720608592</t>
+          <t>4393720463795</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 1700 DeFrost White</t>
+          <t>Стиральная машина Weissgauff WM 4106 D</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -3308,17 +3308,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>439616</t>
+          <t>438965</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>4393720607533</t>
+          <t>4393720605676</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 1760 LowFrost Dark Grey</t>
+          <t>Стиральная машина Weissgauff WM 41106 Inverter Steam</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3338,17 +3338,17 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>440055</t>
+          <t>438977</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>4393720608547</t>
+          <t>4393720605744</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 180 Total NoFrost Dark Grey</t>
+          <t>Стиральная машина Weissgauff WM 4427 Inverter Steam</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3368,17 +3368,17 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>433056</t>
+          <t>439707</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>4393720477488</t>
+          <t>4393720607861</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 185 Total NoFrost Inverter Inox</t>
+          <t>Стиральная машина Weissgauff WM 4506 Inverter Steam</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -3398,17 +3398,17 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>437278</t>
+          <t>431369</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>4393720603375</t>
+          <t>4393720473282</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 2000 Total NoFrost Inverter Black</t>
+          <t>Стиральная машина Weissgauff WM 4506 LED</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -3428,17 +3428,17 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>433060</t>
+          <t>432584</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>4393720477525</t>
+          <t>4393720476603</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 2000 Total NoFrost Inverter Inox</t>
+          <t>Стиральная машина Weissgauff WM 45127 DC Inverter Steam</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -3458,17 +3458,17 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>441084</t>
+          <t>440454</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>4610509420399</t>
+          <t>4393720609124</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 2010 D Inverter NoFrost White</t>
+          <t>Стиральная машина Weissgauff WM 45128 Full Touch Inverter Steam</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -3488,17 +3488,17 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>440695</t>
+          <t>430972</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>4640213440079</t>
+          <t>4393720472933</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 2010 DX Inverter Total NoFrost</t>
+          <t>Стиральная машина Weissgauff WM 47147 DC Inverter Steam</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -3518,17 +3518,17 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>442479</t>
+          <t>436615</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>4620446170134</t>
+          <t>4393720602798</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK 2010 Inox Inverter NoFrost</t>
+          <t>Стиральная машина Weissgauff WM 47147 DC Inverter Steam Silver</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -3548,17 +3548,17 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>442523</t>
+          <t>434363</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>4640213440512</t>
+          <t>4393720601111</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRK-85 Defrost White</t>
+          <t>Стиральная машина Weissgauff WM 4748 Inverter Steam</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -3578,17 +3578,17 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>433024</t>
+          <t>438973</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>4393720477297</t>
+          <t>4393720605706</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Холодильник Weissgauff WRKI 195 Total NoFrost Inverter</t>
+          <t>Стиральная машина Weissgauff WM 48128 Inverter Steam</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Холодильник</t>
+          <t>Стиральная машина</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -3608,35 +3608,1655 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
+          <t>438974</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>4393720605713</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 48128 Inverter Steam Grey</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Стиральная машина</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>441512</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>4393720610472</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 49128 Сolor Touch Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Стиральная машина</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>441460</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>4393720610977</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 56411 Color Touch Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Стиральная машина</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>436159</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>4393720602538</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 58411 Direct Drive Inverter Premium Steam Steel</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Стиральная машина</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>438332</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>4393720604471</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 591410 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Стиральная машина</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>434764</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>4393720601203</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 59411 Direct Drive Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Стиральная машина</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>433622</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>4393720600671</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 46148 DC Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Стиральная машина</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>439118</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>4393720606352</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 46148 DC Inverter Steam Black</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Стиральная машина</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>438586</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>4393720605232</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 4628 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Стиральная машина</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>430970</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>4393720472919</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 47148 DC Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Стиральная машина</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>433417</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>4393720600381</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 58411 Direct Drive Inverter Premium Steam Grey</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Стиральная машина</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>440884</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>4393720609902</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 995 Autodose Direct Drive Touch</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Стиральная машина</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>441342</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>4393720610304</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 486 Compact Air Grey</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Сушильная машина</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>438786</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>4393720605799</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 4948 Heat Pump</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Сушильная машина</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>433780</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>4393720600787</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 6110 B Heat Pump</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Сушильная машина</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>438504</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>4393720605188</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 6128 B Heat Pump</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Сушильная машина</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>429679</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>4393720467670</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 6128 D</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Сушильная машина</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>432450</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>4393720476504</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 998 Heat Pump Full Touch Silver</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Сушильная машина</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>437284</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>4393720603320</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WCD 450 B NoFrost Inverter</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>433144</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>4393720477433</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WFD 450 Built-in Inverter NoFrost Dark Inox</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>440025</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>4393720608561</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WR 1450 DeFrost</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>439610</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>4393720607472</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WR-092 Defrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>441036</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>4393720609995</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRI-85 Inverter</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>442653</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>4670239260764</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1180 Defrost White</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>440021</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>4393720608608</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1275 DeFrost White</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>442280</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>4670239260177</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1300 Defrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>439613</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>4393720607502</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1430 Defrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>440022</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>4393720608615</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 145 DeFrost Inox</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>440023</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>4393720608622</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 145 DeFrost White</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>442651</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>4670239260832</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1480 Defrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>442964</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>4670239260887</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1520 Defrost Black</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>439569</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>4393720607113</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1520 Defrost Silver</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>439568</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>4393720607106</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1520 Defrost White</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>442286</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>4670239260238</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1650 Defrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>440028</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>4393720608585</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1700 DeFrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>440027</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>4393720608592</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1700 DeFrost White</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>439616</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>4393720607533</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1760 LowFrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>440055</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>4393720608547</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 180 Total NoFrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>439620</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>4393720607571</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1800 Defrost White</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>433056</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>4393720477488</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 185 Total NoFrost Inverter Inox</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>433055</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>4393720477471</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 185 Total NoFrost Inverter White</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>437278</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>4393720603375</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2000 Total NoFrost Inverter Black</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>437283</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>4393720603429</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2000 Total NoFrost Inverter Bru Steel Glass</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>433060</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>4393720477525</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2000 Total NoFrost Inverter Inox</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>441112</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>4610509420382</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2010 D Inverter NoFrost Beige Soft Close</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>441084</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>4610509420399</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2010 D Inverter NoFrost White</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>442480</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>4620446170141</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2010 Dark Grey Inverter NoFrost</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>444579</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>4610509420986</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2010 Defrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>440695</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>4640213440079</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2010 DX Inverter Total NoFrost</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>439582</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>4393720607281</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2010 Full NoFrost Inverter Dark Grey</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>442479</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>4620446170134</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2010 Inox Inverter NoFrost</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>442523</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>4640213440512</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK-85 Defrost White</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>433024</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>4393720477297</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRKI 195 Total NoFrost Inverter</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>430812</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>4393720472261</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WSBS 600 BG NoFrost Inverter</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Холодильник</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Weissgauff</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
           <t>431526</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B161" s="3" t="inlineStr">
         <is>
           <t>4393720473992</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Холодильник Weissgauff WSBS 600 XB NoFrost Inverter Water Dispenser</t>
         </is>
       </c>
-      <c r="D107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" t="inlineStr">
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" t="inlineStr">
         <is>
           <t>Холодильник</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H107"/>
+  <autoFilter ref="A2:H161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>